--- a/output/pdf_financials_xlsx/ZEN.xlsx
+++ b/output/pdf_financials_xlsx/ZEN.xlsx
@@ -1332,22 +1332,22 @@
         <v>3.524807</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-3.86865</v>
@@ -1378,16 +1378,16 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.509544</v>
+        <v>-3.548988</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.623115</v>
+        <v>-2.701711</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.3393</v>
+        <v>-5.04322</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.049614</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1622,34 +1622,34 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.029266</v>
+        <v>-2.029266</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.039298</v>
+        <v>-1.039298</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.35196</v>
+        <v>-2.35196</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.524807</v>
+        <v>-3.524807</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>-3.86865</v>
@@ -1798,34 +1798,34 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.029266</v>
+        <v>-2.029266</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.039298</v>
+        <v>-1.039298</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.35196</v>
+        <v>-2.35196</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.524807</v>
+        <v>-3.524807</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>-3.86865</v>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-50.73165</v>
+        <v>50.73165</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2136,22 +2136,22 @@
         <v>3.524807</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-3.86865</v>
@@ -2254,22 +2254,22 @@
         <v>3.524807</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-3.86865</v>
@@ -2382,34 +2382,34 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>33.52876381338166</v>
+        <v>233.5287638133817</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>37.48256299728166</v>
+        <v>162.5174370027183</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12.60747753840209</v>
+        <v>187.3925224615979</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -7446,40 +7446,40 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.497769</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-4.025323</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-2.41361</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-9.177210000000001</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-1.672729</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.051471</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.870656</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.4338</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.73518</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.506001</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.316698</v>
       </c>
       <c r="O118" s="3" t="n">
         <v>0</v>
@@ -8962,7 +8962,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>0.007</v>
       </c>
@@ -23252,7 +23256,11 @@
           <t>Mineral exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -29080,7 +29088,11 @@
           <t>Mineral exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -40350,31 +40362,31 @@
         </is>
       </c>
       <c r="G327" s="5" t="n">
-        <v>1.039298</v>
+        <v>-1.039298</v>
       </c>
       <c r="H327" s="5" t="n">
-        <v>2.35196</v>
+        <v>-2.35196</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>3.524807</v>
+        <v>-3.524807</v>
       </c>
       <c r="J327" s="5" t="n">
-        <v>3.015706</v>
+        <v>-3.015706</v>
       </c>
       <c r="K327" s="5" t="n">
-        <v>4.197806</v>
+        <v>-4.197806</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>2.840621</v>
+        <v>-2.840621</v>
       </c>
       <c r="M327" s="5" t="n">
-        <v>1.564521</v>
+        <v>-1.564521</v>
       </c>
       <c r="N327" s="5" t="n">
-        <v>2.428153</v>
+        <v>-2.428153</v>
       </c>
       <c r="O327" s="5" t="n">
-        <v>1.540877</v>
+        <v>-1.540877</v>
       </c>
       <c r="P327" t="inlineStr">
         <is>
@@ -42669,10 +42681,10 @@
         </is>
       </c>
       <c r="F351" s="5" t="n">
-        <v>2.029266</v>
+        <v>-2.029266</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>1.039298</v>
+        <v>-1.039298</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ZEN.xlsx
+++ b/output/pdf_financials_xlsx/ZEN.xlsx
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000184</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.025844</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1119,19 +1119,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.020597</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.510257</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.405483</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.101613</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.040308</v>
       </c>
     </row>
     <row r="13">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.519722</v>
+        <v>1.493878</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.662413</v>
@@ -2157,19 +2157,19 @@
         <v>-3.86865</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-31.694048</v>
+        <v>-31.714645</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-14.414266</v>
+        <v>-14.924523</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-11.70399</v>
+        <v>-12.109473</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-10.039658</v>
+        <v>-10.141271</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-9.767958</v>
+        <v>-9.808266</v>
       </c>
     </row>
     <row r="28">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.519722</v>
+        <v>1.493878</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.662413</v>
@@ -2275,19 +2275,19 @@
         <v>-3.86865</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-31.694048</v>
+        <v>-31.714645</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-14.414266</v>
+        <v>-14.924523</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-11.70399</v>
+        <v>-12.109473</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-10.039658</v>
+        <v>-10.141271</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-9.767958</v>
+        <v>-9.808266</v>
       </c>
     </row>
     <row r="30">
@@ -2355,19 +2355,19 @@
         <v>-164273.8853503185</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-9330.945104897164</v>
+        <v>-9337.009002961733</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-19784.86857456592</v>
+        <v>-20485.24191887997</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-39254.05822377247</v>
+        <v>-40614.00925677489</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-1150.683728846584</v>
+        <v>-1162.329984699053</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-5882.611052225862</v>
+        <v>-5906.885960686067</v>
       </c>
     </row>
     <row r="31">
@@ -2524,37 +2524,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.119186</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.550379</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.112185</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5.316645</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.62663</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.132485</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.169598</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.383968</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.096738</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.221492</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.805947</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
@@ -2640,37 +2640,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.119186</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.550379</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.112185</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5.316645</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.62663</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.132485</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.169598</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.383968</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.096738</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.221492</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.805947</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.52637</v>
+        <v>0.407184</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9.122177000000001</v>
+        <v>8.571797999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.690097</v>
+        <v>2.577912</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.645626</v>
+        <v>1.328981</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.961279</v>
+        <v>1.334649</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.394587</v>
+        <v>0.262102</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.461745</v>
+        <v>0.292147</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.051797</v>
+        <v>0.667829</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.144204</v>
+        <v>0.047466</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.249376</v>
+        <v>0.027884</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.9965349999999999</v>
+        <v>0.190588</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>3.385378</v>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -35287,7 +35287,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -38665,7 +38665,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E358" s="5" t="n">

--- a/output/pdf_financials_xlsx/ZEN.xlsx
+++ b/output/pdf_financials_xlsx/ZEN.xlsx
@@ -7137,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Q112" s="3" t="n">
         <v>0</v>
@@ -22161,7 +22161,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZEN.xlsx
+++ b/output/pdf_financials_xlsx/ZEN.xlsx
@@ -811,19 +811,19 @@
         <v>0.444322</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.401717</v>
+        <v>1.511831</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.970594</v>
+        <v>2.152633</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.523796</v>
+        <v>1.666618</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.958963</v>
+        <v>1.065661</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.840005</v>
+        <v>0.937743</v>
       </c>
     </row>
     <row r="8">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.0054</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-3.548988</v>
+        <v>-0.2777</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-2.701711</v>
@@ -1652,10 +1652,10 @@
         <v>-1.540877</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-3.86865</v>
+        <v>-4.31372</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-31.694048</v>
+        <v>-12.562665</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-14.414266</v>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>233.5287638133817</v>
+        <v>18.27307889206052</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>162.5174370027183</v>
@@ -2734,19 +2734,19 @@
         <v>0</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>0.314375</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0</v>
+        <v>0.106458</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>0.001439</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>0.806353</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0</v>
+        <v>0.051029</v>
       </c>
     </row>
     <row r="38">
@@ -2914,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.027292</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.050908</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.024225</v>
       </c>
     </row>
     <row r="41">
@@ -2966,19 +2966,19 @@
         <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.314375</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.106458</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.028731</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.8572610000000001</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.075254</v>
       </c>
     </row>
     <row r="42">
@@ -3372,19 +3372,19 @@
         <v>3.385378</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>31.959099</v>
+        <v>31.644724</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>17.953009</v>
+        <v>17.846551</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>6.248953</v>
+        <v>6.220222</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>4.246412</v>
+        <v>3.389151</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.974514</v>
+        <v>0.8992599999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4298,55 +4298,55 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.000338</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.6714639999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.998574</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.460914</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.187331</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.155922</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.066037</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.0583</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.127035</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.621642</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.390896</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.348103</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>1.044587</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.911477</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.541311</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>2.006918</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>2.084152</v>
       </c>
     </row>
     <row r="65">
@@ -4472,55 +4472,55 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.072563</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.380997</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.627951</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.439346</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.879378</v>
       </c>
     </row>
     <row r="68">
@@ -4548,19 +4548,19 @@
         <v>0.180922</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.09103700000000001</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.152035</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.6466420000000001</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.415896</v>
       </c>
       <c r="M68" s="3" t="n">
         <v>0.373103</v>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.033107</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.09975299999999999</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.148901</v>
+        <v>0.115794</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.033933</v>
+        <v>-0.06582</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.117381</v>
       </c>
     </row>
     <row r="111">
@@ -7040,34 +7040,34 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.030308</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.070079</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00864</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014377</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003287</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002205</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003041</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00344</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.103211</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>-0.254282</v>
@@ -8414,34 +8414,34 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.030308</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.070079</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00864</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014377</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003287</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002205</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003041</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00344</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.103211</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>-0.254282</v>
@@ -8474,34 +8474,34 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.08456</v>
+        <v>-1.114868</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.317792</v>
+        <v>-1.387871</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.640185</v>
+        <v>-1.648825</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.385803</v>
+        <v>-2.40018</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-1.24636</v>
+        <v>-1.249647</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.68181</v>
+        <v>-1.684015</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.710072</v>
+        <v>-1.713113</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.999855</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.183545</v>
+        <v>-1.186985</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.356386</v>
+        <v>-1.459597</v>
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
@@ -19128,7 +19128,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -23955,7 +23959,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -26402,7 +26410,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -28993,7 +29005,11 @@
           <t>Deferred tax (recovery)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -29387,7 +29403,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -30799,7 +30819,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" s="5" t="n">
         <v>-0.0054</v>
       </c>
@@ -31102,7 +31126,11 @@
           <t>GST/HST receivable</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E233" s="5" t="n">
         <v>-0.033107</v>
       </c>
@@ -34270,7 +34298,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -38164,7 +38196,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -41375,7 +41411,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -42373,7 +42413,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -43575,7 +43619,11 @@
           <t>Future income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" s="5" t="n">
         <v>0.0054</v>
       </c>
